--- a/Exc2/Проверочный лист для аудита ИБ.xlsx
+++ b/Exc2/Проверочный лист для аудита ИБ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -37,6 +37,9 @@
     <t xml:space="preserve">I. Управление доступом</t>
   </si>
   <si>
+    <t xml:space="preserve">Есть проблемы с авторизацией, так как уже были жалобы от пользователей, что им отображаются чужие данные.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Используется ли многофакторная аутентификация (MFA) для доступа к критическим системам и сервисам?</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t xml:space="preserve">II. Безопасность данных</t>
   </si>
   <si>
+    <t xml:space="preserve">Система хранит чувствительные данные, защищаемые законом. Важный вопрос, от которого зависит доверие и репутация.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Разработана ли политика классификации данных, и актуализируется ли она в соответствии с действующим законодательством?</t>
   </si>
   <si>
@@ -139,6 +145,9 @@
     <t xml:space="preserve">III. Защита инфраструктуры</t>
   </si>
   <si>
+    <t xml:space="preserve">Система должна обеспечивать высокую доступность, от этого завичит комфорт жителей. Проблемы в защите инфраструктуры могут отрицательно повлиять на конкурентное преимещество</t>
+  </si>
+  <si>
     <t xml:space="preserve">Используется ли межсетевой экран для ограничения входящего и исходящего трафика?</t>
   </si>
   <si>
@@ -169,6 +178,9 @@
     <t xml:space="preserve">IV.  Управление инцидентами</t>
   </si>
   <si>
+    <t xml:space="preserve">Причины примерно те же, что и в предыдущих разделах. Высокая доступность, чувствительные данные — нужен анализ возможных инцидентов для быстрого выхода из ситуации и исправления ошибок и последствий связанных с защитой.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Используется ли система мониторинга безопасности (SIEM) для корреляции событий и анализа аномалий в режиме реального времени?</t>
   </si>
   <si>
@@ -191,6 +203,9 @@
   </si>
   <si>
     <t xml:space="preserve">1. Управление оборудованием и физической безопасностью</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Так как есть упоминание про собственные серверы, нужно проанализировать физическую защиту.</t>
   </si>
   <si>
     <t xml:space="preserve">Используются ли системы контроля доступа — биометрия, СКУД — в серверных помещениях?</t>
@@ -212,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -239,9 +254,46 @@
       <charset val="204"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="24"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF006600"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="204"/>
@@ -261,68 +313,23 @@
       <charset val="204"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF0000EE"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF996600"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="204"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="10"/>
-      <color rgb="FF0000EE"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF006600"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF996600"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFCC0000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="204"/>
@@ -334,30 +341,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
-        <bgColor rgb="FFE2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC0000"/>
-        <bgColor rgb="FF800000"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -375,6 +358,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDDDDDD"/>
         <bgColor rgb="FFDAE3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -427,7 +434,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="37">
+  <cellStyleXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -451,55 +458,52 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -508,11 +512,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -528,7 +532,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -537,30 +541,29 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="23">
+  <cellStyles count="22">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Heading" xfId="20"/>
-    <cellStyle name="Heading 1" xfId="21"/>
-    <cellStyle name="Heading 2" xfId="22"/>
-    <cellStyle name="Text" xfId="23"/>
-    <cellStyle name="Note" xfId="24"/>
-    <cellStyle name="Footnote" xfId="25"/>
-    <cellStyle name="Hyperlink" xfId="26"/>
-    <cellStyle name="Status" xfId="27"/>
-    <cellStyle name="Good" xfId="28"/>
-    <cellStyle name="Neutral" xfId="29"/>
-    <cellStyle name="Bad" xfId="30"/>
-    <cellStyle name="Warning" xfId="31"/>
-    <cellStyle name="Error" xfId="32"/>
-    <cellStyle name="Accent" xfId="33"/>
-    <cellStyle name="Accent 1" xfId="34"/>
-    <cellStyle name="Accent 2" xfId="35"/>
-    <cellStyle name="Accent 3" xfId="36"/>
+    <cellStyle name="Accent 1 14" xfId="20"/>
+    <cellStyle name="Accent 13" xfId="21"/>
+    <cellStyle name="Accent 2 15" xfId="22"/>
+    <cellStyle name="Accent 3 16" xfId="23"/>
+    <cellStyle name="Bad 10" xfId="24"/>
+    <cellStyle name="Error 12" xfId="25"/>
+    <cellStyle name="Footnote 5" xfId="26"/>
+    <cellStyle name="Good 8" xfId="27"/>
+    <cellStyle name="Heading 1 1" xfId="28"/>
+    <cellStyle name="Heading 2 2" xfId="29"/>
+    <cellStyle name="Hyperlink 6" xfId="30"/>
+    <cellStyle name="Neutral 9" xfId="31"/>
+    <cellStyle name="Note 4" xfId="32"/>
+    <cellStyle name="Status 7" xfId="33"/>
+    <cellStyle name="Text 3" xfId="34"/>
+    <cellStyle name="Warning 11" xfId="35"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -630,12 +633,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C3:F49"/>
+  <dimension ref="C3:G49"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.5"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.71"/>
@@ -663,19 +666,22 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
+      <c r="G4" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="83.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -683,13 +689,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="80.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -697,10 +703,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5"/>
     </row>
@@ -709,13 +715,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -723,10 +729,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="5"/>
     </row>
@@ -735,10 +741,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="5"/>
     </row>
@@ -747,10 +753,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="5"/>
     </row>
@@ -759,10 +765,10 @@
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="5"/>
     </row>
@@ -771,7 +777,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -781,10 +787,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="5"/>
     </row>
@@ -793,13 +799,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -807,10 +813,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="5"/>
     </row>
@@ -819,32 +825,35 @@
         <v>13</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
+      <c r="G18" s="0" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F19" s="5"/>
     </row>
@@ -853,10 +862,10 @@
         <v>2</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F20" s="5"/>
     </row>
@@ -865,10 +874,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="5"/>
     </row>
@@ -877,13 +886,13 @@
         <v>4</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="125.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -891,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -901,7 +910,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -911,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -921,7 +930,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -931,28 +940,31 @@
         <v>9</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
+      <c r="G28" s="0" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="69" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29" s="5"/>
     </row>
@@ -961,9 +973,11 @@
         <v>2</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="F30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="80.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -971,9 +985,11 @@
         <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="F31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -981,9 +997,11 @@
         <v>4</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="F32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="80.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -991,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -1001,7 +1019,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -1011,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -1021,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -1031,25 +1049,30 @@
         <v>9</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="F37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C38" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
+      <c r="G38" s="0" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C39" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -1059,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -1069,7 +1092,7 @@
         <v>3</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1079,7 +1102,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1089,7 +1112,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -1099,14 +1122,14 @@
         <v>6</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -1114,22 +1137,25 @@
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C46" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
+      <c r="G46" s="0" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C47" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1137,7 +1163,7 @@
         <v>2</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
@@ -1147,7 +1173,7 @@
         <v>3</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
